--- a/Fornecedores.xlsx
+++ b/Fornecedores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,41 +435,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fazenda São José</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Distribuidora Nacional</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Atacadão das Frutas</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Posto de Combustível Rafinha</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AutoPosto Mite</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
